--- a/e2e/downloadedFile/sub_Master_Daftar_Gaji.xlsx
+++ b/e2e/downloadedFile/sub_Master_Daftar_Gaji.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="29">
   <si>
     <t>NIK</t>
   </si>
@@ -47,91 +47,61 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>Citra</t>
+    <t>ADROALDINO DA SILVA NORONHA TOME</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>AGOSTINHO GOMES FERNANDES</t>
+  </si>
+  <si>
+    <t>Expat</t>
+  </si>
+  <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>CLAUDIO DA COSTA ALVES</t>
+  </si>
+  <si>
+    <t>DIAN EVIYANTI APLUGI</t>
   </si>
   <si>
     <t>III</t>
   </si>
   <si>
-    <t>Expat</t>
-  </si>
-  <si>
-    <t>dominika</t>
-  </si>
-  <si>
-    <t>IV</t>
-  </si>
-  <si>
-    <t>Santos</t>
+    <t>AHMAD RIYANA SAPUTRA</t>
+  </si>
+  <si>
+    <t>FRIESCA AMELIA</t>
+  </si>
+  <si>
+    <t>HERU YULIANTO</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>RIMBUN SIBURIAN</t>
+  </si>
+  <si>
+    <t>SYALDY KHARISMA ANANDA</t>
+  </si>
+  <si>
+    <t>Lestari Putri Cantika</t>
   </si>
   <si>
     <t>V</t>
   </si>
   <si>
-    <t>Local</t>
-  </si>
-  <si>
-    <t>HELENA</t>
-  </si>
-  <si>
-    <t>II</t>
-  </si>
-  <si>
     <t>Homestaff</t>
-  </si>
-  <si>
-    <t>DEDY EDWARD AMBARITA</t>
-  </si>
-  <si>
-    <t>ADRIANTO LEBRE</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>AHMAD RIYANA SAPUTRA</t>
-  </si>
-  <si>
-    <t>0000002</t>
-  </si>
-  <si>
-    <t>Syifa Hadju</t>
-  </si>
-  <si>
-    <t>ALCINO DE FATIMA M. VALENTE</t>
-  </si>
-  <si>
-    <t>VI</t>
-  </si>
-  <si>
-    <t>CELIA MARIA REGO DE FATIMA</t>
-  </si>
-  <si>
-    <t>ADROALDINO DA SILVA NORONHA TOME</t>
-  </si>
-  <si>
-    <t>Outsource</t>
-  </si>
-  <si>
-    <t>DIAN EVIYANTI APLUGI</t>
-  </si>
-  <si>
-    <t>FRIESCA AMELIA</t>
-  </si>
-  <si>
-    <t>HERU YULIANTO</t>
-  </si>
-  <si>
-    <t>SYALDY KHARISMA ANANDA</t>
-  </si>
-  <si>
-    <t>RIMBUN SIBURIAN</t>
-  </si>
-  <si>
-    <t>Lestari Putri Cantika</t>
-  </si>
-  <si>
-    <t>AGOSTINHO GOMES FERNANDES</t>
   </si>
 </sst>
 </file>
@@ -471,10 +441,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="38.848" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="5.856" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="11.711" bestFit="true" customWidth="true" style="0"/>
@@ -520,7 +490,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2">
-        <v>900145</v>
+        <v>24016</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -532,59 +502,59 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>140</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3">
-        <v>83005</v>
+        <v>26013</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
       <c r="E3">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>90</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4">
-        <v>85014</v>
+        <v>92003</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
@@ -593,536 +563,280 @@
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>90</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5">
-        <v>84016</v>
+        <v>24005</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>145</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6">
-        <v>85006</v>
+        <v>79001</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E6">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7">
-        <v>88015</v>
+        <v>95008</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E7">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>230</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8">
-        <v>83008</v>
+        <v>91009</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>60</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9">
-        <v>95008</v>
+        <v>74003</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
       </c>
       <c r="E9">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="F9">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>260</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>25</v>
+      <c r="A10">
+        <v>81010</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
         <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E10">
-        <v>57</v>
+        <v>500</v>
       </c>
       <c r="F10">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>90</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11">
-        <v>26014</v>
+        <v>91015</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12">
-        <v>92003</v>
+        <v>999999</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E12">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F12">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13">
-        <v>24016</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13">
-        <v>120</v>
-      </c>
-      <c r="F13">
-        <v>10</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>50</v>
-      </c>
-      <c r="J13">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14">
-        <v>79001</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14">
-        <v>200</v>
-      </c>
-      <c r="F14">
-        <v>50</v>
-      </c>
-      <c r="G14">
-        <v>50</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15">
-        <v>91009</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15">
-        <v>500</v>
-      </c>
-      <c r="F15">
-        <v>150</v>
-      </c>
-      <c r="G15">
-        <v>50</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16">
-        <v>74003</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16">
-        <v>500</v>
-      </c>
-      <c r="F16">
-        <v>150</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>50</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17">
-        <v>91015</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17">
-        <v>200</v>
-      </c>
-      <c r="F17">
-        <v>50</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>20</v>
-      </c>
-      <c r="I17">
-        <v>30</v>
-      </c>
-      <c r="J17">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18">
-        <v>81010</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18">
-        <v>500</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="J18">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19">
-        <v>999999</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19">
-        <v>500</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="J19">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20">
-        <v>26013</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20">
-        <v>500</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="J20">
         <v>500</v>
       </c>
     </row>
